--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
   <si>
     <t>48970</t>
   </si>
@@ -129,25 +129,25 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>FFBA073E7C4A8BD35483A828B1751F77</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>543755216</t>
-  </si>
-  <si>
-    <t>4655021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/1er_Trimestre/Publicacion%20de%20Presupuesto%20COBAT-2022/Presupuesto%20De%20Ingresos%20y%20Egresos%202022%20COBAT.pdf</t>
+    <t>67532F07072BDC3565D7D1A7345AC615</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>564688046</t>
+  </si>
+  <si>
+    <t>8033143</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/1er%20Trimestre/Publicacion%20de%20Presupuesto/PRESUPUESTO%202023.pdf</t>
   </si>
   <si>
     <t>https://www.transparenciapresupuestaria.gob.mx/</t>
@@ -156,7 +156,10 @@
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
-    <t>25/04/2022</t>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>26/12/2022</t>
   </si>
   <si>
     <t/>
@@ -183,7 +186,55 @@
     <t>Presupuesto por capítulo de gasto</t>
   </si>
   <si>
-    <t>235894F216DC39E23261339A8584E394</t>
+    <t>80E6B21D23632D1E87705F3F198E56AA</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Materiales y suministros</t>
+  </si>
+  <si>
+    <t>9112031</t>
+  </si>
+  <si>
+    <t>80E6B21D23632D1EB4DBE9155F58B439</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Servicios generales</t>
+  </si>
+  <si>
+    <t>44875950</t>
+  </si>
+  <si>
+    <t>80E6B21D23632D1EA7DE26CBA6A21BBC</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>Transferencias, asignaciones, subsidios y otras ayudas</t>
+  </si>
+  <si>
+    <t>1400000</t>
+  </si>
+  <si>
+    <t>80E6B21D23632D1ED1C12275CA74A3EE</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Bienes muebles e inmuebles</t>
+  </si>
+  <si>
+    <t>8093964</t>
+  </si>
+  <si>
+    <t>BC90D95B5BC25CD50C238BA0D722129D</t>
   </si>
   <si>
     <t>1000</t>
@@ -192,55 +243,7 @@
     <t>Servicios personales</t>
   </si>
   <si>
-    <t>482935413</t>
-  </si>
-  <si>
-    <t>235894F216DC39E25B1E71F5263E65A8</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>Materiales y suministros</t>
-  </si>
-  <si>
-    <t>8968534</t>
-  </si>
-  <si>
-    <t>235894F216DC39E29F29CAEA43FB648E</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>Servicios generales</t>
-  </si>
-  <si>
-    <t>44664539</t>
-  </si>
-  <si>
-    <t>235894F216DC39E28A7E5E5B1A2871B9</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>Transferencias, asignaciones, subsidios y otras ayudas</t>
-  </si>
-  <si>
-    <t>1400000</t>
-  </si>
-  <si>
-    <t>9ECC9B23D0F2FA702E4C8FDD18BD5708</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>Bienes muebles e inmuebles</t>
-  </si>
-  <si>
-    <t>5786730</t>
+    <t>501206101</t>
   </si>
 </sst>
 </file>
@@ -639,13 +642,13 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="226.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="169.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="77.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -843,10 +846,10 @@
         <v>46</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +872,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.85546875" bestFit="1" customWidth="1"/>
@@ -888,28 +891,28 @@
     </row>
     <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -917,16 +920,16 @@
         <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -934,16 +937,16 @@
         <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -951,16 +954,16 @@
         <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -968,16 +971,16 @@
         <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -985,16 +988,16 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
